--- a/referencia/formularios/exemplos/exemplo-loteamento-vale-do-sol-preliminar.xlsx
+++ b/referencia/formularios/exemplos/exemplo-loteamento-vale-do-sol-preliminar.xlsx
@@ -591,7 +591,7 @@
     <row r="2" ht="92" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Como preencher: só as células AMARELAS da coluna B. Cinza-claro com valor em negrito = fixo do tipo de estudo (não editar); cinza com itálico = calculado pelo Excel, só para conferir (não editar). * = obrigatório. PERCENTUAL: digite como porcentagem (4% ou 4 numa célula já formatada em %; nunca 0,04 num campo sem formato). Números sem separador de milhar e com ponto decimal quando digitados fora do Excel. CAMPO COM VÁRIAS UNIDADES: há uma linha por unidade — preencha UMA só e deixe as outras em branco; o Excel não converte uma na outra. Listas (produtos, custos…) têm vagas numeradas; vaga totalmente em branco = sem item.</t>
+          <t>Como preencher: só as células AMARELAS da coluna B. Cinza-claro com valor em negrito = fixo do tipo de estudo (não editar); cinza com itálico = calculado pelo Excel, só para conferir (não editar). * = obrigatório. PERCENTUAL: digite como porcentagem (4% ou 4 numa célula já formatada em %). O Excel guarda 0,04; a API do app espera pontos (4) e o importador converte pelo FORMATO da célula — por isso não troque o formato das células. Números sem separador de milhar e com ponto decimal quando digitados fora do Excel. CAMPO COM VÁRIAS UNIDADES: há uma linha por unidade — preencha UMA só e deixe as outras em branco; o Excel não converte uma na outra. Listas (produtos, custos…) têm vagas numeradas; vaga totalmente em branco = sem item.</t>
         </is>
       </c>
     </row>

--- a/referencia/formularios/exemplos/exemplo-loteamento-vale-do-sol-preliminar.xlsx
+++ b/referencia/formularios/exemplos/exemplo-loteamento-vale-do-sol-preliminar.xlsx
@@ -703,7 +703,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>lista: manual (inserir novo) | nucleo (buscar terreno)</t>
+          <t>lista: manual (inserir novo) | nucleo (buscar terreno — o importador só aceita manual)</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">

--- a/referencia/formularios/exemplos/exemplo-loteamento-vale-do-sol-preliminar.xlsx
+++ b/referencia/formularios/exemplos/exemplo-loteamento-vale-do-sol-preliminar.xlsx
@@ -591,7 +591,7 @@
     <row r="2" ht="92" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Como preencher: só as células AMARELAS da coluna B. Cinza-claro com valor em negrito = fixo do tipo de estudo (não editar); cinza com itálico = calculado pelo Excel, só para conferir (não editar). * = obrigatório. PERCENTUAL: digite como porcentagem (4% ou 4 numa célula já formatada em %). O Excel guarda 0,04; a API do app espera pontos (4) e o importador converte pelo FORMATO da célula — por isso não troque o formato das células. Números sem separador de milhar e com ponto decimal quando digitados fora do Excel. CAMPO COM VÁRIAS UNIDADES: há uma linha por unidade — preencha UMA só e deixe as outras em branco; o Excel não converte uma na outra. Listas (produtos, custos…) têm vagas numeradas; vaga totalmente em branco = sem item.</t>
+          <t>Como preencher: só as células AMARELAS da coluna B. Cinza-claro com valor em negrito = fixo do tipo de estudo (não editar); cinza com itálico = calculado pelo Excel, só para conferir (não editar). * = obrigatório. PERCENTUAL: digite com o símbolo % (4%), nunca só o número. O Excel guarda 0,04; a API do app espera pontos (4) e o importador converte pelo FORMATO da célula — por isso não troque o formato das células. Números sem separador de milhar e com ponto decimal quando digitados fora do Excel. CAMPO COM VÁRIAS UNIDADES: há uma linha por unidade — preencha UMA só e deixe as outras em branco; o Excel não converte uma na outra. Listas (produtos, custos…) têm vagas numeradas; vaga totalmente em branco = sem item.</t>
         </is>
       </c>
     </row>
